--- a/Email_Storage.xlsx
+++ b/Email_Storage.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,16 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>last_contacted_date</t>
         </is>
@@ -431,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>abc@abc.com</t>
+          <t>a.anderson@salesforce.com</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -439,7 +451,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>koolrahulmj04@gmailsss.com</t>
+          <t>a.clark@deeplearning.ai</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -447,10 +459,3186 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>xyz@gmail.com</t>
+          <t>a.hernandez@snowflake.com</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>a.hill@scale.com</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>a.jackson@accenture.com</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>a.kumar@nvidia.com</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>a.miller@nvidia.com</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>a.thompson@wipro.com</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>a.verma@amazon.com</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>a.walker@nextgensoft.net</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>a.williams@amazon.com</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>a.wright@intel.com</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>alex.allen@oracle.com</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>alex.b@meta.com</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>alex.d@openai.com</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>alex.f@huggingface.co</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>alex.g@meta.com</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>alex.gonzalez@uber.com</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>alex.harris@techcorp.io</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>alex.jones@apple.com</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>alex.l@stripe.com</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>alex.lee@tcs.com</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>alex.lewis@datasolutions.org</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>alex.m@capgemini.com</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>alex.m@openai.com</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>alex.nair@anthropic.com</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>alex.r@cloudscale.co</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>alex.reddy@apple.com</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>alex.rodriguez@anthropic.com</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>alex.s@qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>alex.sharma@google.com</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>alex.smith@google.com</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>alex.t@adobe.com</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>alex.taylor@spotify.com</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>alex.torres@broadcom.com</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>alex.w@cognizant.com</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>alex.y@apexsystems.com</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>alex_garcia@netflix.com</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>alex_iyer@databricks.com</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>alex_johnson@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>alex_king@cisco.com</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>alex_martinez@databricks.com</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>alex_moore@ibm.com</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>alex_nguyen@palantir.com</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>alex_patel@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>alex_perez@infosys.com</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>alex_robinson@quantumai.tech</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>alex_sanchez@innovatetech.com</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>alex_singh@netflix.com</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>alex_wilson@airbnb.com</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>careers@accenture.com</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>careers@adobe.com</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>careers@airbnb.com</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>careers@amazon.com</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>careers@anthropic.com</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>careers@apexsystems.com</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>careers@apple.com</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>careers@broadcom.com</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>careers@capgemini.com</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>careers@cisco.com</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>careers@cloudscale.co</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>careers@cognizant.com</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>careers@databricks.com</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>careers@datasolutions.org</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>careers@deeplearning.ai</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>careers@google.com</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>careers@huggingface.co</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>careers@ibm.com</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>careers@infosys.com</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>careers@innovatetech.com</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>careers@intel.com</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>careers@meta.com</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>careers@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>careers@netflix.com</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>careers@nextgensoft.net</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>careers@nvidia.com</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>careers@openai.com</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>careers@oracle.com</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>careers@palantir.com</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>careers@qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>careers@quantumai.tech</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>careers@salesforce.com</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>careers@scale.com</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>careers@snowflake.com</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>careers@spotify.com</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>careers@stripe.com</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>careers@tcs.com</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>careers@techcorp.io</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>careers@uber.com</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>careers@wipro.com</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>d.anderson@salesforce.com</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>d.clark@deeplearning.ai</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>d.hernandez@snowflake.com</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>d.hill@scale.com</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>d.jackson@accenture.com</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>d.kumar@nvidia.com</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>d.miller@nvidia.com</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>d.thompson@wipro.com</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>d.verma@amazon.com</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>d.walker@nextgensoft.net</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>d.williams@amazon.com</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>d.wright@intel.com</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>david.allen@oracle.com</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>david.b@meta.com</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>david.d@openai.com</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>david.f@huggingface.co</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>david.g@meta.com</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>david.gonzalez@uber.com</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>david.harris@techcorp.io</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>david.jones@apple.com</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>david.l@stripe.com</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>david.lee@tcs.com</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>david.lewis@datasolutions.org</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>david.m@capgemini.com</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>david.m@openai.com</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>david.nair@anthropic.com</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>david.r@cloudscale.co</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>david.reddy@apple.com</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>david.rodriguez@anthropic.com</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>david.s@qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>david.sharma@google.com</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>david.smith@google.com</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>david.t@adobe.com</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>david.taylor@spotify.com</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>david.torres@broadcom.com</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>david.w@cognizant.com</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>david.y@apexsystems.com</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>david_garcia@netflix.com</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>david_iyer@databricks.com</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>david_johnson@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>david_king@cisco.com</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>david_martinez@databricks.com</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>david_moore@ibm.com</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>david_nguyen@palantir.com</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>david_patel@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>david_perez@infosys.com</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>david_robinson@quantumai.tech</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>david_sanchez@innovatetech.com</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>david_singh@netflix.com</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>david_wilson@airbnb.com</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>e.allen@wipro.com</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>e.gonzalez@amazon.com</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>e.harris@salesforce.com</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>e.jones@intel.com</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>e.lee@snowflake.com</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>e.lewis@accenture.com</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>e.nair@scale.com</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>e.reddy@intel.com</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>e.rodriguez@scale.com</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>e.sharma@nextgensoft.net</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>e.smith@nextgensoft.net</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>e.taylor@nvidia.com</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>e.torres@deeplearning.ai</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>emily.anderson@apple.com</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>emily.clark@spotify.com</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>emily.g@qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>emily.hernandez@google.com</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>emily.hill@datasolutions.org</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>emily.i@huggingface.co</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>emily.j@apexsystems.com</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>emily.jackson@anthropic.com</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>emily.k@cognizant.com</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>emily.kumar@broadcom.com</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>emily.m@huggingface.co</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>emily.m@openai.com</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>emily.miller@broadcom.com</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>emily.n@cloudscale.co</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>emily.p@apexsystems.com</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>emily.p@stripe.com</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>emily.r@capgemini.com</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>emily.s@adobe.com</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>emily.s@qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>emily.thompson@uber.com</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>emily.verma@oracle.com</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>emily.w@meta.com</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>emily.walker@tcs.com</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>emily.williams@oracle.com</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>emily.wright@techcorp.io</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>emily_brown@cisco.com</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>emily_davis@palantir.com</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>emily_flores@quantumai.tech</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>emily_gupta@cisco.com</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>emily_lopez@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>emily_martin@databricks.com</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>emily_mehta@palantir.com</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>emily_ramirez@ibm.com</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>emily_scott@innovatetech.com</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>emily_thomas@netflix.com</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>emily_white@airbnb.com</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>emily_young@infosys.com</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>m.anderson@intel.com</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>m.clark@nvidia.com</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>m.hernandez@nextgensoft.net</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>m.hill@accenture.com</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>m.jackson@scale.com</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>m.kumar@deeplearning.ai</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>m.miller@deeplearning.ai</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>m.thompson@amazon.com</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>m.verma@wipro.com</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>m.walker@snowflake.com</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>m.williams@wipro.com</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>m.wright@salesforce.com</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>michael.allen@uber.com</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>michael.b@cognizant.com</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>michael.d@cloudscale.co</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>michael.f@capgemini.com</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>michael.g@cognizant.com</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>michael.gonzalez@oracle.com</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>michael.harris@apple.com</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>michael.jones@techcorp.io</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>michael.l@apexsystems.com</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>michael.lee@google.com</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>michael.lewis@anthropic.com</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>michael.m@cloudscale.co</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>michael.m@huggingface.co</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>michael.nair@datasolutions.org</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>michael.r@openai.com</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>michael.reddy@techcorp.io</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>michael.rodriguez@datasolutions.org</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>michael.s@adobe.com</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>michael.sharma@tcs.com</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>michael.smith@tcs.com</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>michael.t@qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>michael.taylor@broadcom.com</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>michael.torres@spotify.com</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>michael.w@meta.com</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>michael.y@stripe.com</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>michael_garcia@innovatetech.com</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>michael_iyer@quantumai.tech</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>michael_johnson@infosys.com</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>michael_king@airbnb.com</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>michael_martinez@quantumai.tech</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>michael_moore@palantir.com</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>michael_nguyen@ibm.com</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>michael_patel@infosys.com</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>michael_perez@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>michael_robinson@databricks.com</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>michael_sanchez@netflix.com</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>michael_singh@innovatetech.com</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>michael_wilson@cisco.com</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>p.gonzalez@wipro.com</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>p.harris@intel.com</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>p.jones@salesforce.com</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>p.lee@nextgensoft.net</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>p.lewis@scale.com</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>p.rodriguez@accenture.com</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>p.smith@snowflake.com</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>p.taylor@deeplearning.ai</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>priya.anderson@techcorp.io</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>priya.clark@broadcom.com</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>priya.g@adobe.com</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>priya.hernandez@tcs.com</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>priya.j@stripe.com</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>priya.jackson@datasolutions.org</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>priya.m@capgemini.com</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>priya.m@cloudscale.co</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>priya.miller@spotify.com</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>priya.p@apexsystems.com</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>priya.r@huggingface.co</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>priya.s@qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>priya.thompson@oracle.com</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>priya.w@cognizant.com</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>priya.williams@uber.com</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>priya_brown@airbnb.com</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>priya_davis@ibm.com</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>priya_lopez@infosys.com</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>priya_martin@quantumai.tech</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>priya_ramirez@palantir.com</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>priya_thomas@innovatetech.com</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>priya_white@cisco.com</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>recruiting@accenture.com</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>recruiting@adobe.com</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>recruiting@airbnb.com</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>recruiting@amazon.com</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>recruiting@anthropic.com</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>recruiting@apexsystems.com</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>recruiting@apple.com</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>recruiting@broadcom.com</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>recruiting@capgemini.com</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>recruiting@cisco.com</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>recruiting@cloudscale.co</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>recruiting@cognizant.com</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>recruiting@databricks.com</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>recruiting@datasolutions.org</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>recruiting@deeplearning.ai</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>recruiting@google.com</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>recruiting@huggingface.co</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>recruiting@ibm.com</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>recruiting@infosys.com</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>recruiting@innovatetech.com</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>recruiting@intel.com</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>recruiting@meta.com</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>recruiting@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>recruiting@netflix.com</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>recruiting@nextgensoft.net</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>recruiting@nvidia.com</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>recruiting@openai.com</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>recruiting@oracle.com</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>recruiting@palantir.com</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>recruiting@qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>recruiting@quantumai.tech</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>recruiting@salesforce.com</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>recruiting@scale.com</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>recruiting@snowflake.com</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>recruiting@spotify.com</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>recruiting@stripe.com</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>recruiting@tcs.com</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>recruiting@techcorp.io</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>recruiting@uber.com</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>recruiting@wipro.com</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>s.allen@amazon.com</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>s.gonzalez@wipro.com</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>s.harris@intel.com</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>s.jones@salesforce.com</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>s.lee@nextgensoft.net</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>s.lewis@scale.com</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>s.nair@accenture.com</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>s.reddy@salesforce.com</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>s.rodriguez@accenture.com</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>s.sharma@snowflake.com</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>s.smith@snowflake.com</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>s.taylor@deeplearning.ai</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>s.torres@nvidia.com</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>sarah.anderson@techcorp.io</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>sarah.clark@broadcom.com</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>sarah.g@adobe.com</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>sarah.hernandez@tcs.com</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>sarah.hill@anthropic.com</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>sarah.i@capgemini.com</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>sarah.j@stripe.com</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>sarah.jackson@datasolutions.org</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>sarah.k@meta.com</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>sarah.kumar@spotify.com</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>sarah.m@capgemini.com</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>sarah.m@cloudscale.co</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>sarah.miller@spotify.com</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>sarah.n@openai.com</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>sarah.p@apexsystems.com</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>sarah.p@stripe.com</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>sarah.r@huggingface.co</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>sarah.s@adobe.com</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>sarah.s@qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>sarah.thompson@oracle.com</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>sarah.verma@uber.com</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>sarah.w@cognizant.com</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>sarah.walker@google.com</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>sarah.williams@uber.com</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>sarah.wright@apple.com</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>sarah_brown@airbnb.com</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>sarah_davis@ibm.com</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>sarah_flores@databricks.com</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>sarah_gupta@airbnb.com</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>sarah_lopez@infosys.com</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>sarah_martin@quantumai.tech</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>sarah_mehta@ibm.com</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>sarah_ramirez@palantir.com</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>sarah_scott@netflix.com</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>sarah_thomas@innovatetech.com</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>sarah_white@cisco.com</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>sarah_young@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>talent@accenture.com</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>talent@adobe.com</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>talent@airbnb.com</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>talent@amazon.com</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>talent@anthropic.com</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>talent@apexsystems.com</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>talent@apple.com</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>talent@broadcom.com</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>talent@capgemini.com</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>talent@cisco.com</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>talent@cloudscale.co</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>talent@cognizant.com</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>talent@databricks.com</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>talent@datasolutions.org</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>talent@deeplearning.ai</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>talent@google.com</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>talent@huggingface.co</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>talent@ibm.com</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>talent@infosys.com</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>talent@innovatetech.com</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>talent@intel.com</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>talent@meta.com</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>talent@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>talent@netflix.com</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>talent@nextgensoft.net</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>talent@nvidia.com</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>talent@openai.com</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>talent@oracle.com</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>talent@palantir.com</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>talent@qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>talent@quantumai.tech</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>talent@salesforce.com</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>talent@scale.com</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>talent@snowflake.com</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>talent@spotify.com</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>talent@stripe.com</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>talent@tcs.com</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>talent@techcorp.io</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>talent@uber.com</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>talent@wipro.com</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
